--- a/InputData/ccs/CC/CCS Calculations.xlsx
+++ b/InputData/ccs/CC/CCS Calculations.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\ccs\CC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Modeling\EPS\US\eps-us\InputData\ccs\CC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BAC8057-3D10-459B-A73B-36B6485E5AC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C8FFF93-ACC1-4A89-AA71-AD1CFE45439B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="60840" yWindow="2385" windowWidth="24900" windowHeight="14490" firstSheet="5" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="102">
   <si>
     <t>Source:</t>
   </si>
@@ -363,6 +363,18 @@
   </si>
   <si>
     <t>hydrogen electrolysis in our BAU case.</t>
+  </si>
+  <si>
+    <t>green hydrogen</t>
+  </si>
+  <si>
+    <t>low carbon hydrogen</t>
+  </si>
+  <si>
+    <t>green hydrogen if</t>
+  </si>
+  <si>
+    <t>low carbon hydrogen if</t>
   </si>
 </sst>
 </file>
@@ -899,7 +911,7 @@
   <sheetPr codeName="Sheet11">
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="26.7265625" customWidth="1"/>
@@ -907,7 +919,7 @@
     <col min="4" max="4" width="11.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="58" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" ht="58" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>95</v>
       </c>
@@ -941,8 +953,14 @@
       <c r="K1" s="7" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L1" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="M1" s="7" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -978,8 +996,14 @@
       <c r="K2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -1015,8 +1039,14 @@
       <c r="K3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -1052,8 +1082,14 @@
       <c r="K4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -1089,8 +1125,14 @@
       <c r="K5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -1126,8 +1168,14 @@
       <c r="K6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -1163,8 +1211,14 @@
       <c r="K7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -1200,8 +1254,14 @@
       <c r="K8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -1237,8 +1297,14 @@
       <c r="K9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -1275,8 +1341,14 @@
       <c r="K10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -1312,8 +1384,14 @@
       <c r="K11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -1349,8 +1427,14 @@
       <c r="K12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -1386,8 +1470,14 @@
       <c r="K13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -1423,8 +1513,14 @@
       <c r="K14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>22</v>
       </c>
@@ -1460,8 +1556,14 @@
       <c r="K15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>23</v>
       </c>
@@ -1497,8 +1599,14 @@
       <c r="K16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>24</v>
       </c>
@@ -1534,8 +1642,14 @@
       <c r="K17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -1571,8 +1685,14 @@
       <c r="K18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>26</v>
       </c>
@@ -1608,8 +1728,14 @@
       <c r="K19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>27</v>
       </c>
@@ -1645,8 +1771,14 @@
       <c r="K20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>28</v>
       </c>
@@ -1682,8 +1814,14 @@
       <c r="K21">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>29</v>
       </c>
@@ -1719,8 +1857,14 @@
       <c r="K22">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>30</v>
       </c>
@@ -1756,8 +1900,14 @@
       <c r="K23">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>31</v>
       </c>
@@ -1793,8 +1943,14 @@
       <c r="K24">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>32</v>
       </c>
@@ -1830,8 +1986,14 @@
       <c r="K25">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>33</v>
       </c>
@@ -1865,6 +2027,12 @@
         <v>0</v>
       </c>
       <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
         <v>0</v>
       </c>
     </row>
@@ -1878,7 +2046,7 @@
   <sheetPr codeName="Sheet13">
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="26.7265625" customWidth="1"/>
@@ -1978,6 +2146,22 @@
         <v>94</v>
       </c>
       <c r="B11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A12" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A13" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="B13">
         <v>0</v>
       </c>
     </row>
@@ -3807,7 +3991,7 @@
   <sheetPr codeName="Sheet10">
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="46.81640625" customWidth="1"/>
@@ -3815,7 +3999,7 @@
     <col min="4" max="4" width="11.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="58" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" ht="58" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>95</v>
       </c>
@@ -3849,8 +4033,14 @@
       <c r="K1" s="7" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L1" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="M1" s="7" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -3886,8 +4076,14 @@
       <c r="K2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -3923,8 +4119,14 @@
       <c r="K3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -3960,8 +4162,14 @@
       <c r="K4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -3997,8 +4205,14 @@
       <c r="K5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -4034,8 +4248,14 @@
       <c r="K6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -4071,8 +4291,14 @@
       <c r="K7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -4108,8 +4334,14 @@
       <c r="K8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -4145,8 +4377,14 @@
       <c r="K9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -4182,8 +4420,14 @@
       <c r="K10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -4219,8 +4463,14 @@
       <c r="K11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -4256,8 +4506,14 @@
       <c r="K12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -4293,8 +4549,14 @@
       <c r="K13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -4330,8 +4592,14 @@
       <c r="K14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>22</v>
       </c>
@@ -4367,8 +4635,14 @@
       <c r="K15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>23</v>
       </c>
@@ -4404,8 +4678,14 @@
       <c r="K16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>24</v>
       </c>
@@ -4441,8 +4721,14 @@
       <c r="K17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -4478,8 +4764,14 @@
       <c r="K18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>26</v>
       </c>
@@ -4515,8 +4807,14 @@
       <c r="K19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>27</v>
       </c>
@@ -4552,8 +4850,14 @@
       <c r="K20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>28</v>
       </c>
@@ -4589,8 +4893,14 @@
       <c r="K21">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>29</v>
       </c>
@@ -4626,8 +4936,14 @@
       <c r="K22">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>30</v>
       </c>
@@ -4663,8 +4979,14 @@
       <c r="K23">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>31</v>
       </c>
@@ -4700,8 +5022,14 @@
       <c r="K24">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>32</v>
       </c>
@@ -4737,8 +5065,14 @@
       <c r="K25">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>33</v>
       </c>
@@ -4772,6 +5106,12 @@
         <v>0</v>
       </c>
       <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
         <v>0</v>
       </c>
     </row>

--- a/InputData/ccs/CC/CCS Calculations.xlsx
+++ b/InputData/ccs/CC/CCS Calculations.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26827"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Modeling\EPS\US\eps-us\InputData\ccs\CC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\ccs\CC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C8FFF93-ACC1-4A89-AA71-AD1CFE45439B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BAC8057-3D10-459B-A73B-36B6485E5AC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="60840" yWindow="2385" windowWidth="24900" windowHeight="14490" firstSheet="5" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="98">
   <si>
     <t>Source:</t>
   </si>
@@ -363,18 +363,6 @@
   </si>
   <si>
     <t>hydrogen electrolysis in our BAU case.</t>
-  </si>
-  <si>
-    <t>green hydrogen</t>
-  </si>
-  <si>
-    <t>low carbon hydrogen</t>
-  </si>
-  <si>
-    <t>green hydrogen if</t>
-  </si>
-  <si>
-    <t>low carbon hydrogen if</t>
   </si>
 </sst>
 </file>
@@ -911,7 +899,7 @@
   <sheetPr codeName="Sheet11">
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="26.7265625" customWidth="1"/>
@@ -919,7 +907,7 @@
     <col min="4" max="4" width="11.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="58" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" ht="58" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>95</v>
       </c>
@@ -953,14 +941,8 @@
       <c r="K1" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="L1" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="M1" s="7" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -996,14 +978,8 @@
       <c r="K2">
         <v>0</v>
       </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -1039,14 +1015,8 @@
       <c r="K3">
         <v>0</v>
       </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -1082,14 +1052,8 @@
       <c r="K4">
         <v>0</v>
       </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -1125,14 +1089,8 @@
       <c r="K5">
         <v>0</v>
       </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -1168,14 +1126,8 @@
       <c r="K6">
         <v>0</v>
       </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -1211,14 +1163,8 @@
       <c r="K7">
         <v>0</v>
       </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -1254,14 +1200,8 @@
       <c r="K8">
         <v>0</v>
       </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -1297,14 +1237,8 @@
       <c r="K9">
         <v>0</v>
       </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -1341,14 +1275,8 @@
       <c r="K10">
         <v>0</v>
       </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -1384,14 +1312,8 @@
       <c r="K11">
         <v>0</v>
       </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -1427,14 +1349,8 @@
       <c r="K12">
         <v>0</v>
       </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
-      <c r="M12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -1470,14 +1386,8 @@
       <c r="K13">
         <v>0</v>
       </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -1513,14 +1423,8 @@
       <c r="K14">
         <v>0</v>
       </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-      <c r="M14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>22</v>
       </c>
@@ -1556,14 +1460,8 @@
       <c r="K15">
         <v>0</v>
       </c>
-      <c r="L15">
-        <v>0</v>
-      </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>23</v>
       </c>
@@ -1599,14 +1497,8 @@
       <c r="K16">
         <v>0</v>
       </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
-      <c r="M16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>24</v>
       </c>
@@ -1642,14 +1534,8 @@
       <c r="K17">
         <v>0</v>
       </c>
-      <c r="L17">
-        <v>0</v>
-      </c>
-      <c r="M17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -1685,14 +1571,8 @@
       <c r="K18">
         <v>0</v>
       </c>
-      <c r="L18">
-        <v>0</v>
-      </c>
-      <c r="M18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>26</v>
       </c>
@@ -1728,14 +1608,8 @@
       <c r="K19">
         <v>0</v>
       </c>
-      <c r="L19">
-        <v>0</v>
-      </c>
-      <c r="M19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>27</v>
       </c>
@@ -1771,14 +1645,8 @@
       <c r="K20">
         <v>0</v>
       </c>
-      <c r="L20">
-        <v>0</v>
-      </c>
-      <c r="M20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>28</v>
       </c>
@@ -1814,14 +1682,8 @@
       <c r="K21">
         <v>0</v>
       </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-      <c r="M21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>29</v>
       </c>
@@ -1857,14 +1719,8 @@
       <c r="K22">
         <v>0</v>
       </c>
-      <c r="L22">
-        <v>0</v>
-      </c>
-      <c r="M22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>30</v>
       </c>
@@ -1900,14 +1756,8 @@
       <c r="K23">
         <v>0</v>
       </c>
-      <c r="L23">
-        <v>0</v>
-      </c>
-      <c r="M23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>31</v>
       </c>
@@ -1943,14 +1793,8 @@
       <c r="K24">
         <v>0</v>
       </c>
-      <c r="L24">
-        <v>0</v>
-      </c>
-      <c r="M24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>32</v>
       </c>
@@ -1986,14 +1830,8 @@
       <c r="K25">
         <v>0</v>
       </c>
-      <c r="L25">
-        <v>0</v>
-      </c>
-      <c r="M25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>33</v>
       </c>
@@ -2027,12 +1865,6 @@
         <v>0</v>
       </c>
       <c r="K26">
-        <v>0</v>
-      </c>
-      <c r="L26">
-        <v>0</v>
-      </c>
-      <c r="M26">
         <v>0</v>
       </c>
     </row>
@@ -2046,7 +1878,7 @@
   <sheetPr codeName="Sheet13">
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="26.7265625" customWidth="1"/>
@@ -2146,22 +1978,6 @@
         <v>94</v>
       </c>
       <c r="B11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A12" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="B12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A13" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="B13">
         <v>0</v>
       </c>
     </row>
@@ -3991,7 +3807,7 @@
   <sheetPr codeName="Sheet10">
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="46.81640625" customWidth="1"/>
@@ -3999,7 +3815,7 @@
     <col min="4" max="4" width="11.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="58" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" ht="58" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>95</v>
       </c>
@@ -4033,14 +3849,8 @@
       <c r="K1" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="L1" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="M1" s="7" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -4076,14 +3886,8 @@
       <c r="K2">
         <v>0</v>
       </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -4119,14 +3923,8 @@
       <c r="K3">
         <v>0</v>
       </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -4162,14 +3960,8 @@
       <c r="K4">
         <v>0</v>
       </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -4205,14 +3997,8 @@
       <c r="K5">
         <v>0</v>
       </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -4248,14 +4034,8 @@
       <c r="K6">
         <v>0</v>
       </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -4291,14 +4071,8 @@
       <c r="K7">
         <v>0</v>
       </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -4334,14 +4108,8 @@
       <c r="K8">
         <v>0</v>
       </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -4377,14 +4145,8 @@
       <c r="K9">
         <v>0</v>
       </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -4420,14 +4182,8 @@
       <c r="K10">
         <v>0</v>
       </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -4463,14 +4219,8 @@
       <c r="K11">
         <v>0</v>
       </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -4506,14 +4256,8 @@
       <c r="K12">
         <v>0</v>
       </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
-      <c r="M12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -4549,14 +4293,8 @@
       <c r="K13">
         <v>0</v>
       </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -4592,14 +4330,8 @@
       <c r="K14">
         <v>0</v>
       </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-      <c r="M14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>22</v>
       </c>
@@ -4635,14 +4367,8 @@
       <c r="K15">
         <v>0</v>
       </c>
-      <c r="L15">
-        <v>0</v>
-      </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>23</v>
       </c>
@@ -4678,14 +4404,8 @@
       <c r="K16">
         <v>0</v>
       </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
-      <c r="M16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>24</v>
       </c>
@@ -4721,14 +4441,8 @@
       <c r="K17">
         <v>0</v>
       </c>
-      <c r="L17">
-        <v>0</v>
-      </c>
-      <c r="M17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -4764,14 +4478,8 @@
       <c r="K18">
         <v>0</v>
       </c>
-      <c r="L18">
-        <v>0</v>
-      </c>
-      <c r="M18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>26</v>
       </c>
@@ -4807,14 +4515,8 @@
       <c r="K19">
         <v>0</v>
       </c>
-      <c r="L19">
-        <v>0</v>
-      </c>
-      <c r="M19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>27</v>
       </c>
@@ -4850,14 +4552,8 @@
       <c r="K20">
         <v>0</v>
       </c>
-      <c r="L20">
-        <v>0</v>
-      </c>
-      <c r="M20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>28</v>
       </c>
@@ -4893,14 +4589,8 @@
       <c r="K21">
         <v>0</v>
       </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-      <c r="M21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>29</v>
       </c>
@@ -4936,14 +4626,8 @@
       <c r="K22">
         <v>0</v>
       </c>
-      <c r="L22">
-        <v>0</v>
-      </c>
-      <c r="M22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>30</v>
       </c>
@@ -4979,14 +4663,8 @@
       <c r="K23">
         <v>0</v>
       </c>
-      <c r="L23">
-        <v>0</v>
-      </c>
-      <c r="M23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>31</v>
       </c>
@@ -5022,14 +4700,8 @@
       <c r="K24">
         <v>0</v>
       </c>
-      <c r="L24">
-        <v>0</v>
-      </c>
-      <c r="M24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>32</v>
       </c>
@@ -5065,14 +4737,8 @@
       <c r="K25">
         <v>0</v>
       </c>
-      <c r="L25">
-        <v>0</v>
-      </c>
-      <c r="M25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>33</v>
       </c>
@@ -5106,12 +4772,6 @@
         <v>0</v>
       </c>
       <c r="K26">
-        <v>0</v>
-      </c>
-      <c r="L26">
-        <v>0</v>
-      </c>
-      <c r="M26">
         <v>0</v>
       </c>
     </row>
